--- a/data/结算汇兑比率.xlsx
+++ b/data/结算汇兑比率.xlsx
@@ -124,17 +124,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0.86381</t>
+          <t>0.86660</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>0.86379</t>
+          <t>0.86660</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -146,17 +146,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0.86552</t>
+          <t>0.86748</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>0.86568</t>
+          <t>0.86772</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -168,17 +168,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.86559</t>
+          <t>0.86766</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0.86561</t>
+          <t>0.86774</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -190,17 +190,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.86603</t>
+          <t>0.86840</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0.86637</t>
+          <t>0.86860</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -212,17 +212,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0.86599</t>
+          <t>0.86595</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0.86601</t>
+          <t>0.86625</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -234,17 +234,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.86783</t>
+          <t>0.86460</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0.86797</t>
+          <t>0.86480</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -256,17 +256,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0.86905</t>
+          <t>0.86554</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0.86935</t>
+          <t>0.86586</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -278,17 +278,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0.86896</t>
+          <t>0.86253</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0.86904</t>
+          <t>0.86247</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -300,17 +300,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0.86837</t>
+          <t>0.86277</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0.86843</t>
+          <t>0.86283</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -322,17 +322,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.86926</t>
+          <t>0.86250</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0.86954</t>
+          <t>0.86250</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -344,17 +344,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>0.86576</t>
+          <t>0.86311</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0.86684</t>
+          <t>0.86309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -366,17 +366,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>0.86691</t>
+          <t>0.86510</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0.86709</t>
+          <t>0.86530</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -388,17 +388,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0.86771</t>
+          <t>0.86508</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0.86809</t>
+          <t>0.86512</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -410,17 +410,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0.86770</t>
+          <t>0.86401</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0.86770</t>
+          <t>0.86399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -432,17 +432,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.86834</t>
+          <t>0.86559</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0.86846</t>
+          <t>0.86641</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -454,17 +454,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0.86804</t>
+          <t>0.86423</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0.86816</t>
+          <t>0.86437</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -476,17 +476,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0.86941</t>
+          <t>0.86478</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0.86959</t>
+          <t>0.86502</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -498,17 +498,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.87146</t>
+          <t>0.86443</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0.87214</t>
+          <t>0.86437</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -520,17 +520,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0.87235</t>
+          <t>0.86248</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0.87245</t>
+          <t>0.86272</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0.87259</t>
+          <t>0.86310</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0.87281</t>
+          <t>0.86310</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>0.87046</t>
+          <t>0.86381</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0.87094</t>
+          <t>0.86379</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>0.87204</t>
+          <t>0.86552</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0.87296</t>
+          <t>0.86568</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>0.87289</t>
+          <t>0.86559</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0.87291</t>
+          <t>0.86561</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>0.87129</t>
+          <t>0.86603</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0.87151</t>
+          <t>0.86637</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0.87058</t>
+          <t>0.86599</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0.87062</t>
+          <t>0.86601</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>0.87069</t>
+          <t>0.86783</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0.87071</t>
+          <t>0.86797</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0.87162</t>
+          <t>0.86905</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0.87198</t>
+          <t>0.86935</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -718,17 +718,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>0.87085</t>
+          <t>0.86896</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0.87115</t>
+          <t>0.86904</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -740,17 +740,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>0.86987</t>
+          <t>0.86837</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0.86993</t>
+          <t>0.86843</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>0.86968</t>
+          <t>0.86926</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0.86972</t>
+          <t>0.86954</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>0.87248</t>
+          <t>0.86576</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0.87272</t>
+          <t>0.86684</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -806,17 +806,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>0.87240</t>
+          <t>0.86691</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0.87240</t>
+          <t>0.86709</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>0.87307</t>
+          <t>0.86771</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0.87313</t>
+          <t>0.86809</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>0.87139</t>
+          <t>0.86770</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0.87181</t>
+          <t>0.86770</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0.87484</t>
+          <t>0.86834</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0.87596</t>
+          <t>0.86846</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -894,17 +894,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>0.87653</t>
+          <t>0.86804</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0.87787</t>
+          <t>0.86816</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>0.88125</t>
+          <t>0.86941</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0.88235</t>
+          <t>0.86959</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>0.88294</t>
+          <t>0.87146</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0.88306</t>
+          <t>0.87214</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>0.88315</t>
+          <t>0.87235</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0.88325</t>
+          <t>0.87245</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -982,17 +982,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>0.88309</t>
+          <t>0.87259</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>0.88311</t>
+          <t>0.87281</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>0.88230</t>
+          <t>0.87046</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>0.88230</t>
+          <t>0.87094</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1026,17 +1026,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>0.87961</t>
+          <t>0.87204</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0.88039</t>
+          <t>0.87296</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1048,17 +1048,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>0.88207</t>
+          <t>0.87289</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0.88333</t>
+          <t>0.87291</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>0.87707</t>
+          <t>0.87129</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0.87933</t>
+          <t>0.87151</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1092,17 +1092,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>0.88069</t>
+          <t>0.87058</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0.88151</t>
+          <t>0.87062</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0.87661</t>
+          <t>0.87069</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>0.87799</t>
+          <t>0.87071</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>0.87893</t>
+          <t>0.87162</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>0.87887</t>
+          <t>0.87198</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1158,17 +1158,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>0.88115</t>
+          <t>0.87085</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0.88185</t>
+          <t>0.87115</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>0.88222</t>
+          <t>0.86987</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0.88218</t>
+          <t>0.86993</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1202,17 +1202,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>0.87783</t>
+          <t>0.86968</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>0.87917</t>
+          <t>0.86972</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1224,17 +1224,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>0.87789</t>
+          <t>0.87248</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>0.87811</t>
+          <t>0.87272</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1246,17 +1246,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>0.87873</t>
+          <t>0.87240</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>0.87867</t>
+          <t>0.87240</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1268,17 +1268,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>0.88522</t>
+          <t>0.87307</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0.88718</t>
+          <t>0.87313</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>0.88130</t>
+          <t>0.87139</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>0.88290</t>
+          <t>0.87181</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>0.88259</t>
+          <t>0.87484</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>0.88261</t>
+          <t>0.87596</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1334,17 +1334,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>0.88423</t>
+          <t>0.87653</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>0.88537</t>
+          <t>0.87787</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1356,17 +1356,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0.88389</t>
+          <t>0.88125</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>0.88391</t>
+          <t>0.88235</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1378,17 +1378,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>0.88009</t>
+          <t>0.88294</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>0.88051</t>
+          <t>0.88306</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1400,17 +1400,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0.87512</t>
+          <t>0.88315</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>0.87648</t>
+          <t>0.88325</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>0.87358</t>
+          <t>0.88309</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>0.87442</t>
+          <t>0.88311</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>0.87729</t>
+          <t>0.88230</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>0.87831</t>
+          <t>0.88230</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1466,17 +1466,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>0.87987</t>
+          <t>0.87961</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>0.87973</t>
+          <t>0.88039</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -1488,17 +1488,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>0.88062</t>
+          <t>0.88207</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>0.88058</t>
+          <t>0.88333</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -1510,17 +1510,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0.88208</t>
+          <t>0.87707</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>0.88312</t>
+          <t>0.87933</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -1532,17 +1532,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>0.88389</t>
+          <t>0.88069</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>0.88391</t>
+          <t>0.88151</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0.88388</t>
+          <t>0.87661</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>0.88392</t>
+          <t>0.87799</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -1576,17 +1576,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0.88594</t>
+          <t>0.87893</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>0.88606</t>
+          <t>0.87887</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -1598,17 +1598,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0.88818</t>
+          <t>0.88115</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>0.88822</t>
+          <t>0.88185</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -1620,17 +1620,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0.88860</t>
+          <t>0.88222</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>0.88860</t>
+          <t>0.88218</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -1642,17 +1642,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0.88735</t>
+          <t>0.87783</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>0.88805</t>
+          <t>0.87917</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -1664,17 +1664,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0.88731</t>
+          <t>0.87789</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>0.88749</t>
+          <t>0.87811</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -1686,17 +1686,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0.88976</t>
+          <t>0.87873</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>0.88984</t>
+          <t>0.87867</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -1708,17 +1708,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0.88970</t>
+          <t>0.88522</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>0.88970</t>
+          <t>0.88718</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -1730,17 +1730,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0.88948</t>
+          <t>0.88130</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>0.88952</t>
+          <t>0.88290</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -1752,17 +1752,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0.88948</t>
+          <t>0.88259</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>0.88952</t>
+          <t>0.88261</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -1774,17 +1774,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0.89186</t>
+          <t>0.88423</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>0.89174</t>
+          <t>0.88537</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0.89200</t>
+          <t>0.88389</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>0.89200</t>
+          <t>0.88391</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -1818,17 +1818,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0.89268</t>
+          <t>0.88009</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>0.89272</t>
+          <t>0.88051</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0.89259</t>
+          <t>0.87512</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>0.89261</t>
+          <t>0.87648</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -1862,17 +1862,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>0.89279</t>
+          <t>0.87358</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>0.89281</t>
+          <t>0.87442</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -1884,17 +1884,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>0.89135</t>
+          <t>0.87729</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>0.89185</t>
+          <t>0.87831</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>0.89250</t>
+          <t>0.87987</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>0.89250</t>
+          <t>0.87973</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -1928,17 +1928,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>0.89318</t>
+          <t>0.88062</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>0.89322</t>
+          <t>0.88058</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -1950,17 +1950,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>0.89348</t>
+          <t>0.88208</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>0.89352</t>
+          <t>0.88312</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>0.89412</t>
+          <t>0.88389</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>0.89428</t>
+          <t>0.88391</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>0.89409</t>
+          <t>0.88388</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>0.89411</t>
+          <t>0.88392</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -2016,17 +2016,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>0.89409</t>
+          <t>0.88594</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>0.89411</t>
+          <t>0.88606</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>0.89569</t>
+          <t>0.88818</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>0.89551</t>
+          <t>0.88822</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2060,17 +2060,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>0.89578</t>
+          <t>0.88860</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>0.89582</t>
+          <t>0.88860</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2082,17 +2082,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>0.89746</t>
+          <t>0.88735</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>0.89754</t>
+          <t>0.88805</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -2104,17 +2104,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>0.89592</t>
+          <t>0.88731</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>0.89628</t>
+          <t>0.88749</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>0.89577</t>
+          <t>0.88976</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>0.89583</t>
+          <t>0.88984</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2148,17 +2148,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>0.89422</t>
+          <t>0.88970</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>0.89478</t>
+          <t>0.88970</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>0.89738</t>
+          <t>0.88948</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>0.89742</t>
+          <t>0.88952</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -2192,17 +2192,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>0.90071</t>
+          <t>0.88948</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>0.90129</t>
+          <t>0.88952</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2214,20 +2214,394 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>0.90143</t>
+          <t>0.89186</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>0.90157</t>
+          <t>0.89174</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>0.89200</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>0.89200</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>0.89268</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>0.89272</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>0.89259</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>0.89261</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>0.89279</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>0.89281</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>0.89135</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>0.89185</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>0.89250</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>0.89250</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>0.89318</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>0.89322</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>0.89348</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>0.89352</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>0.89412</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>0.89428</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>0.89409</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>0.89411</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>0.89409</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>0.89411</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>0.89569</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>0.89551</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>0.89578</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>0.89582</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>0.89746</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>0.89754</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>0.89592</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>0.89628</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>0.89577</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>0.89583</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>0.89422</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>0.89478</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
